--- a/Perceptron_TR.xlsx
+++ b/Perceptron_TR.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Başlangıç" sheetId="1" r:id="Rf4e66550c98046fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametreler" sheetId="2" r:id="Rcdbd8b9703ab4c3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veri Kümesi" sheetId="3" r:id="R49c7173ad5074bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eğitim Adımları" sheetId="4" r:id="R41046c2d1ebe4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epoch Analizi" sheetId="5" r:id="R1d2393e3cdde4758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafikler" sheetId="6" r:id="R176ee37dea8d47cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formüller" sheetId="7" r:id="Rf2992996e20d4c54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teknik Terimler" sheetId="8" r:id="R734f457a4ea048cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Örnek Çözüm" sheetId="9" r:id="R197b3b57aeb142e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Başlangıç" sheetId="1" r:id="R5fdf42a969c942d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametreler" sheetId="2" r:id="Rdc472389825b4a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veri Kümesi" sheetId="3" r:id="Rd1cb71cba3c948d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eğitim Adımları" sheetId="4" r:id="R4f92c4679d874298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epoch Analizi" sheetId="5" r:id="R8ef0517681d14775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafikler" sheetId="6" r:id="R5bcfbb9aecab4877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formüller" sheetId="7" r:id="R2683e3e291fa4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teknik Terimler" sheetId="8" r:id="R8a137f8be3cd4921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Örnek Çözüm" sheetId="9" r:id="R1bbbd9bc770649b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -160,7 +160,7 @@
         <x:color rgb="FFA52A2A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -170,7 +170,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCF5E8"/>
         </x:patternFill>
       </x:fill>
@@ -625,7 +625,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re3073f861b0f4982"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf06715503c924acf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -655,7 +655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1b06a2621d684c63"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb724fe0024c4b04"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -685,7 +685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a11a62ad88949fa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5bfcc2d19b974ae7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -715,7 +715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7e8ec88c6f8e4992"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0077da477d949ec"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8271,7 +8271,7 @@
     <x:mergeCell ref="A3:P3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d8f1df158e04a84"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75f05508e5014071"/>
 </x:worksheet>
 </file>
 
@@ -8336,9 +8336,8 @@
       <x:c r="B6" t="str">
         <x:v>net = w1·x1 + w2·x2 + b</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="e">
-        <x:f>G6*D6+H6*E6+I6</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="C6" s="34" t="str">
+        <x:v>='Eğitim Adımları'!G6*'Eğitim Adımları'!D6+'Eğitim Adımları'!H6*'Eğitim Adımları'!E6+'Eğitim Adımları'!I6</x:v>
       </x:c>
       <x:c r="D6" s="34" t="str">
         <x:v>Ağırlıklı giriş toplamı.</x:v>
@@ -8351,9 +8350,8 @@
       <x:c r="B7" t="str">
         <x:v>ŷ=+1 (net≥0), aksi halde −1</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="n">
-        <x:f>IF(J6&gt;=0,1,-1)</x:f>
-        <x:v>1</x:v>
+      <x:c r="C7" s="34" t="str">
+        <x:v>=IF('Eğitim Adımları'!J6&gt;=0,1,-1)</x:v>
       </x:c>
       <x:c r="D7" s="34" t="str">
         <x:v>Net değeri bipolar sınıf etiketine çevirir.</x:v>
@@ -8366,9 +8364,8 @@
       <x:c r="B8" t="str">
         <x:v>I = 1 (ŷ ≠ t); 0 (ŷ = t)</x:v>
       </x:c>
-      <x:c r="C8" s="34" t="n">
-        <x:f>IF(K6=F6,0,1)</x:f>
-        <x:v>0</x:v>
+      <x:c r="C8" s="34" t="str">
+        <x:v>=IF('Eğitim Adımları'!K6='Eğitim Adımları'!F6,0,1)</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
         <x:v>Güncellemenin yapılıp yapılmayacağını belirler.</x:v>
@@ -8381,9 +8378,8 @@
       <x:c r="B9" t="str">
         <x:v>w1(yeni) = w1 + η·t·x1·I</x:v>
       </x:c>
-      <x:c r="C9" s="34" t="e">
-        <x:f>G6+'Parametreler'!$B$6*F6*D6*L6</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="C9" s="34" t="str">
+        <x:v>='Eğitim Adımları'!G6+'Parametreler'!$B$6*'Eğitim Adımları'!F6*'Eğitim Adımları'!D6*'Eğitim Adımları'!L6</x:v>
       </x:c>
       <x:c r="D9" s="34" t="str">
         <x:v>Hatalı sınıflamada birinci ağırlık güncellenir.</x:v>
@@ -8396,9 +8392,8 @@
       <x:c r="B10" t="str">
         <x:v>w2(yeni) = w2 + η·t·x2·I</x:v>
       </x:c>
-      <x:c r="C10" s="34" t="n">
-        <x:f>H6+'Parametreler'!$B$6*F6*E6*L6</x:f>
-        <x:v>0</x:v>
+      <x:c r="C10" s="34" t="str">
+        <x:v>='Eğitim Adımları'!H6+'Parametreler'!$B$6*'Eğitim Adımları'!F6*'Eğitim Adımları'!E6*'Eğitim Adımları'!L6</x:v>
       </x:c>
       <x:c r="D10" s="34" t="str">
         <x:v>Hatalı sınıflamada ikinci ağırlık güncellenir.</x:v>
@@ -8411,9 +8406,8 @@
       <x:c r="B11" t="str">
         <x:v>b(yeni) = b + η·t·I</x:v>
       </x:c>
-      <x:c r="C11" s="34" t="n">
-        <x:f>I6+'Parametreler'!$B$6*F6*L6</x:f>
-        <x:v>0</x:v>
+      <x:c r="C11" s="34" t="str">
+        <x:v>='Eğitim Adımları'!I6+'Parametreler'!$B$6*'Eğitim Adımları'!F6*'Eğitim Adımları'!L6</x:v>
       </x:c>
       <x:c r="D11" s="34" t="str">
         <x:v>Hatalı sınıflamada bias güncellenir.</x:v>
@@ -8426,9 +8420,8 @@
       <x:c r="B12" t="str">
         <x:v>epoch = ⌊(adım−1)/4⌋+1</x:v>
       </x:c>
-      <x:c r="C12" s="34" t="e">
-        <x:f>INT((A6-1)/'Parametreler'!$B$11)+1</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="C12" s="34" t="str">
+        <x:v>=INT(('Eğitim Adımları'!A6-1)/'Parametreler'!$B$11)+1</x:v>
       </x:c>
       <x:c r="D12" s="34" t="str">
         <x:v>Dört örneğin bir epoch oluşturduğunu gösterir.</x:v>
@@ -8441,9 +8434,8 @@
       <x:c r="B13" t="str">
         <x:v>örnek = ((adım−1) mod 4)+1</x:v>
       </x:c>
-      <x:c r="C13" s="34" t="e">
-        <x:f>MOD(A6-1,'Parametreler'!$B$11)+1</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="C13" s="34" t="str">
+        <x:v>=MOD('Eğitim Adımları'!A6-1,'Parametreler'!$B$11)+1</x:v>
       </x:c>
       <x:c r="D13" s="34" t="str">
         <x:v>Örneklerin sırayla tekrar edilmesini sağlar.</x:v>
@@ -8456,9 +8448,8 @@
       <x:c r="B14" t="str">
         <x:v>x1 = veri[örnek]</x:v>
       </x:c>
-      <x:c r="C14" s="34" t="e">
-        <x:f>INDEX('Veri Kümesi'!$B$6:$B$9,C6)</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="C14" s="34" t="str">
+        <x:v>=INDEX('Veri Kümesi'!$B$6:$B$9,'Eğitim Adımları'!C6)</x:v>
       </x:c>
       <x:c r="D14" s="34" t="str">
         <x:v>Veri kümesinden birinci girişi alır.</x:v>
@@ -8471,9 +8462,8 @@
       <x:c r="B15" t="str">
         <x:v>∑ I (o epoch'ta)</x:v>
       </x:c>
-      <x:c r="C15" s="34" t="n">
-        <x:f>SUMIF('Eğitim Adımları'!$B$6:$B$85,A6,'Eğitim Adımları'!$L$6:$L$85)</x:f>
-        <x:v>0</x:v>
+      <x:c r="C15" s="34" t="str">
+        <x:v>=SUMIF('Eğitim Adımları'!$B$6:$B$85,'Epoch Analizi'!A6,'Eğitim Adımları'!$L$6:$L$85)</x:v>
       </x:c>
       <x:c r="D15" s="34" t="str">
         <x:v>Hatalı eğitim adımlarını sayar.</x:v>
@@ -8486,9 +8476,8 @@
       <x:c r="B16" t="str">
         <x:v>doğru sınıflar / 4</x:v>
       </x:c>
-      <x:c r="C16" s="34" t="n">
-        <x:f>F6/4</x:f>
-        <x:v>0</x:v>
+      <x:c r="C16" s="34" t="str">
+        <x:v>='Epoch Analizi'!F6/4</x:v>
       </x:c>
       <x:c r="D16" s="34" t="str">
         <x:v>Epoch sonu modelinin bütün örneklerdeki doğruluğu.</x:v>
@@ -8529,9 +8518,8 @@
       <x:c r="B19" t="str">
         <x:v>t=+1 yalnız x1=x2=+1 iken</x:v>
       </x:c>
-      <x:c r="C19" s="34" t="n">
-        <x:f>'Veri Kümesi'!D9</x:f>
-        <x:v>1</x:v>
+      <x:c r="C19" s="34" t="str">
+        <x:v>='Veri Kümesi'!D9</x:v>
       </x:c>
       <x:c r="D19" s="34" t="str">
         <x:v>Bipolar mantıksal AND.</x:v>
